--- a/public/designer-data/player_build.xlsx
+++ b/public/designer-data/player_build.xlsx
@@ -2372,9 +2372,6 @@
       <c r="A2" t="s">
         <v>22</v>
       </c>
-      <c r="B2" t="s">
-        <v>6</v>
-      </c>
       <c r="C2" t="s">
         <v>23</v>
       </c>
@@ -2401,9 +2398,6 @@
       <c r="A3" t="s">
         <v>27</v>
       </c>
-      <c r="B3" t="s">
-        <v>6</v>
-      </c>
       <c r="C3" t="s">
         <v>28</v>
       </c>
@@ -2430,9 +2424,6 @@
       <c r="A4" t="s">
         <v>31</v>
       </c>
-      <c r="B4" t="s">
-        <v>6</v>
-      </c>
       <c r="C4" t="s">
         <v>32</v>
       </c>
@@ -2459,9 +2450,6 @@
       <c r="A5" t="s">
         <v>35</v>
       </c>
-      <c r="B5" t="s">
-        <v>6</v>
-      </c>
       <c r="C5" t="s">
         <v>36</v>
       </c>
@@ -2488,9 +2476,6 @@
       <c r="A6" t="s">
         <v>37</v>
       </c>
-      <c r="B6" t="s">
-        <v>6</v>
-      </c>
       <c r="C6" t="s">
         <v>38</v>
       </c>
@@ -2516,9 +2501,6 @@
     <row r="7" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>39</v>
-      </c>
-      <c r="B7" t="s">
-        <v>6</v>
       </c>
       <c r="C7" t="s">
         <v>40</v>

--- a/public/designer-data/player_build.xlsx
+++ b/public/designer-data/player_build.xlsx
@@ -131,10 +131,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -166,10 +166,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="Ã¯Â¼Â­Ã¯Â¼Â³ Ã¯Â¼Â°Ã£ÂÂ´Ã£ÂÂ·Ã£ÂÂÃ£ÂÂ¯"/>
-        <a:font script="Hang" typeface="Ã«Â§ÂÃ¬ÂÂ ÃªÂ³Â Ã«ÂÂ"/>
-        <a:font script="Hans" typeface="Ã¥Â®ÂÃ¤Â½Â"/>
-        <a:font script="Hant" typeface="Ã¦ÂÂ°Ã§Â´Â°Ã¦ÂÂÃ©Â«Â"/>
+        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -479,7 +479,7 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F27"/>
+  <dimension ref="A1:F35"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1021,17 +1021,177 @@
         <v>8</v>
       </c>
     </row>
+    <row r="28">
+      <c r="A28" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B28" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C28" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D28" t="str">
+        <v>1</v>
+      </c>
+      <c r="E28" t="str">
+        <v>druid_bear_t_growl</v>
+      </c>
+      <c r="F28">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B29" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C29" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D29" t="str">
+        <v>2</v>
+      </c>
+      <c r="E29" t="str">
+        <v>druid_bear_t_mangle</v>
+      </c>
+      <c r="F29">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B30" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C30" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D30" t="str">
+        <v>3</v>
+      </c>
+      <c r="E30" t="str">
+        <v>druid_bear_t_thrash</v>
+      </c>
+      <c r="F30">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B31" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C31" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D31" t="str">
+        <v>4</v>
+      </c>
+      <c r="E31" t="str">
+        <v>druid_bear_t_skull_bash</v>
+      </c>
+      <c r="F31">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B32" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C32" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D32" t="str">
+        <v>Q</v>
+      </c>
+      <c r="E32" t="str">
+        <v>druid_bear_t_ironfur</v>
+      </c>
+      <c r="F32">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B33" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C33" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D33" t="str">
+        <v>E</v>
+      </c>
+      <c r="E33" t="str">
+        <v>druid_bear_t_frenzied_regeneration</v>
+      </c>
+      <c r="F33">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B34" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C34" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D34" t="str">
+        <v>R</v>
+      </c>
+      <c r="E34" t="str">
+        <v>druid_bear_t_swipe</v>
+      </c>
+      <c r="F34">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B35" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C35" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D35" t="str">
+        <v>F</v>
+      </c>
+      <c r="E35" t="str">
+        <v>druid_bear_t_moonfire</v>
+      </c>
+      <c r="F35">
+        <v>8</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F27"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F35"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:F17"/>
+  <dimension ref="A1:F22"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -1264,7 +1424,7 @@
         <v>druid_bear_t</v>
       </c>
       <c r="D12" t="str">
-        <v>druid_bear_t_pack_presence</v>
+        <v>druid_bear_t_mark_of_the_wild</v>
       </c>
       <c r="E12" t="b">
         <v>1</v>
@@ -1370,13 +1530,113 @@
         <v>1</v>
       </c>
       <c r="F17">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B18" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C18" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D18" t="str">
+        <v>druid_bear_t_great_bear_vigor</v>
+      </c>
+      <c r="E18" t="b">
+        <v>1</v>
+      </c>
+      <c r="F18">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B19" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C19" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D19" t="str">
+        <v>druid_bear_t_thick_hide</v>
+      </c>
+      <c r="E19" t="b">
+        <v>1</v>
+      </c>
+      <c r="F19">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B20" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C20" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D20" t="str">
+        <v>druid_bear_t_savage_focus</v>
+      </c>
+      <c r="E20" t="b">
+        <v>1</v>
+      </c>
+      <c r="F20">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B21" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C21" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D21" t="str">
+        <v>druid_bear_t_skull_bash_instinct</v>
+      </c>
+      <c r="E21" t="b">
+        <v>1</v>
+      </c>
+      <c r="F21">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="B22" t="str">
+        <v>8slot_1</v>
+      </c>
+      <c r="C22" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="D22" t="str">
+        <v>druid_bear_t_mark_of_the_wild</v>
+      </c>
+      <c r="E22" t="b">
+        <v>1</v>
+      </c>
+      <c r="F22">
         <v>5</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:F17"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:F22"/>
   </ignoredErrors>
 </worksheet>
 </file>
@@ -2712,7 +2972,7 @@
         <v>裂伤</v>
       </c>
       <c r="E19" t="str">
-        <v>成功释放获得20点怒气并产生高额单体仇恨。</v>
+        <v>成功释放获得15点怒气并产生高额单体仇恨。</v>
       </c>
       <c r="F19" t="str">
         <v>druid_bear_t_mangle_pic</v>
@@ -2774,7 +3034,7 @@
         <v>痛击</v>
       </c>
       <c r="E20" t="str">
-        <v>对3x3范围造成伤害和仇恨，成功释放获得15点怒气。</v>
+        <v>对3x3范围造成10点伤害和仇恨，成功释放获得10点怒气。</v>
       </c>
       <c r="F20" t="str">
         <v>druid_bear_t_thrash_pic</v>
@@ -2786,7 +3046,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>8000</v>
+        <v>9000</v>
       </c>
       <c r="J20">
         <v>0</v>
@@ -2836,7 +3096,7 @@
         <v>打断</v>
       </c>
       <c r="E21" t="str">
-        <v>打断当前目标施法，成功打断可由天赋获得额外怒气。</v>
+        <v>打断当前目标施法，不消耗怒气；成功打断可由天赋获得额外怒气。</v>
       </c>
       <c r="F21" t="str">
         <v>druid_bear_t_skull_bash_pic</v>
@@ -2845,7 +3105,7 @@
         <v>4</v>
       </c>
       <c r="H21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="I21">
         <v>12000</v>
@@ -2898,7 +3158,7 @@
         <v>铁鬃</v>
       </c>
       <c r="E22" t="str">
-        <v>消耗怒气叠加只对物理伤害生效的减伤，最多3层。</v>
+        <v>消耗20点怒气叠加物理伤害减免，默认每层20%且最多3层。</v>
       </c>
       <c r="F22" t="str">
         <v>druid_bear_t_ironfur_pic</v>
@@ -2907,7 +3167,7 @@
         <v>4</v>
       </c>
       <c r="H22">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I22">
         <v>0</v>
@@ -2969,10 +3229,10 @@
         <v>4</v>
       </c>
       <c r="H23">
-        <v>35</v>
+        <v>20</v>
       </c>
       <c r="I23">
-        <v>24000</v>
+        <v>18000</v>
       </c>
       <c r="J23">
         <v>0</v>
@@ -3084,7 +3344,7 @@
         <v>月火</v>
       </c>
       <c r="E25" t="str">
-        <v>对当前目标施加持续伤害，不消耗怒气。</v>
+        <v>成功释放获得5点怒气；对当前目标立即造成5点伤害，并在12秒内每3秒造成5点伤害。</v>
       </c>
       <c r="F25" t="str">
         <v>druid_bear_t_moonfire_pic</v>
@@ -3096,7 +3356,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>10000</v>
+        <v>15000</v>
       </c>
       <c r="J25">
         <v>0</v>
@@ -3146,7 +3406,7 @@
         <v>树皮</v>
       </c>
       <c r="E26" t="str">
-        <v>自身获得6秒全伤害减伤，结束时可由天赋驱散减益。</v>
+        <v>自身获得10秒30%全伤害减伤，结束时可由天赋驱散减益。</v>
       </c>
       <c r="F26" t="str">
         <v>druid_bear_t_barkskin_pic</v>
@@ -3158,7 +3418,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>28000</v>
+        <v>30000</v>
       </c>
       <c r="J26">
         <v>0</v>
@@ -3247,7 +3507,7 @@
         <v>10</v>
       </c>
       <c r="R27" t="str">
-        <v>WF-5解锁</v>
+        <v>ZA-3解锁</v>
       </c>
       <c r="S27" t="str">
         <v/>
@@ -3332,7 +3592,7 @@
         <v>化身</v>
       </c>
       <c r="E29" t="str">
-        <v>短时间提高最大生命值、物理减伤和仇恨稳定性。</v>
+        <v>短时间提高最大生命值和仇恨稳定性。</v>
       </c>
       <c r="F29" t="str">
         <v>druid_bear_t_incarnation_ursoc_pic</v>
@@ -3394,7 +3654,7 @@
         <v>沉睡</v>
       </c>
       <c r="E30" t="str">
-        <v>自身获得全伤害减伤，并将部分承伤转化为反击伤害与仇恨。</v>
+        <v>成功释放获得25点怒气；自身获得10秒25%最大生命值和25%全伤害减伤，并将部分承伤转化为反击伤害与仇恨。</v>
       </c>
       <c r="F30" t="str">
         <v>druid_bear_t_rage_of_the_sleeper_pic</v>
@@ -3433,7 +3693,7 @@
         <v>13</v>
       </c>
       <c r="R30" t="str">
-        <v>ZA-3解锁</v>
+        <v>WF-5解锁</v>
       </c>
       <c r="S30" t="str">
         <v/>
@@ -4540,7 +4800,7 @@
         <v>15</v>
       </c>
       <c r="G21">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="H21">
         <v>0</v>
@@ -4558,7 +4818,7 @@
         <v>player</v>
       </c>
       <c r="M21" t="str">
-        <v>裂伤伤害并在成功释放后获得20怒气。</v>
+        <v>裂伤伤害并在成功释放后获得15怒气。</v>
       </c>
       <c r="N21" t="b">
         <v>1</v>
@@ -4584,7 +4844,7 @@
         <v>10</v>
       </c>
       <c r="G22">
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="H22">
         <v>0</v>
@@ -4596,13 +4856,13 @@
         <v>0</v>
       </c>
       <c r="K22">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L22" t="str">
         <v>player</v>
       </c>
       <c r="M22" t="str">
-        <v>痛击对3x3范围产生伤害和仇恨。</v>
+        <v>痛击对3x3范围造成10点伤害和仇恨，成功释放后获得10怒。</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -4668,7 +4928,7 @@
       <c r="E24" t="str">
         <v>self</v>
       </c>
-      <c r="F24" t="str">
+      <c r="F24">
         <v>20</v>
       </c>
       <c r="G24">
@@ -4690,7 +4950,7 @@
         <v>player</v>
       </c>
       <c r="M24" t="str">
-        <v>每层20%物理减伤，最多3层。</v>
+        <v>默认每层20%物理伤害减免，最多3层。</v>
       </c>
       <c r="N24" t="b">
         <v>1</v>
@@ -4801,7 +5061,7 @@
         <v>cross</v>
       </c>
       <c r="F27">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="G27">
         <v>0</v>
@@ -4816,13 +5076,13 @@
         <v>0</v>
       </c>
       <c r="K27">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="L27" t="str">
         <v>player</v>
       </c>
       <c r="M27" t="str">
-        <v>横扫只受GCD限制。</v>
+        <v>横扫对cross范围造成8点伤害和仇恨，只受公共GCD限制。</v>
       </c>
       <c r="N27" t="b">
         <v>1</v>
@@ -4845,7 +5105,7 @@
         <v>current</v>
       </c>
       <c r="F28">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="G28">
         <v>3</v>
@@ -4857,16 +5117,16 @@
         <v>druid_bear_t_moonfire</v>
       </c>
       <c r="J28">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="K28">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="L28" t="str">
         <v>player</v>
       </c>
       <c r="M28" t="str">
-        <v>月火术12秒持续伤害，每3秒一跳。</v>
+        <v>成功释放获得5怒；立即造成5点伤害，随后3/6/9/12秒各造成5点伤害；每次伤害5倍仇恨。</v>
       </c>
       <c r="N28" t="b">
         <v>1</v>
@@ -4892,10 +5152,10 @@
         <v>0</v>
       </c>
       <c r="G29">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="H29">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="I29" t="str">
         <v>druid_bear_t_barkskin</v>
@@ -4910,7 +5170,7 @@
         <v>player</v>
       </c>
       <c r="M29" t="str">
-        <v>6秒20%全伤害减伤。</v>
+        <v>10秒30%全伤害减伤。</v>
       </c>
       <c r="N29" t="b">
         <v>1</v>
@@ -5068,10 +5328,10 @@
         <v>0.35</v>
       </c>
       <c r="G33">
-        <v>0.2</v>
+        <v>0</v>
       </c>
       <c r="H33">
-        <v>12000</v>
+        <v>30000</v>
       </c>
       <c r="I33" t="str">
         <v>druid_bear_t_incarnation_ursoc</v>
@@ -5086,7 +5346,7 @@
         <v>player</v>
       </c>
       <c r="M33" t="str">
-        <v>12秒最大生命值+35%和20%物理减伤。</v>
+        <v>30秒最大生命值+35%；期间熊T技能仇恨倍率提高30%。</v>
       </c>
       <c r="N33" t="b">
         <v>1</v>
@@ -5115,7 +5375,7 @@
         <v>0.25</v>
       </c>
       <c r="H34">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="I34" t="str">
         <v>druid_bear_t_rage_of_the_sleeper</v>
@@ -5130,7 +5390,7 @@
         <v>player</v>
       </c>
       <c r="M34" t="str">
-        <v>8秒25%全伤害减伤和反击。</v>
+        <v>10秒25%全伤害减伤、反击和25%最大生命值提升；成功释放获得25怒。</v>
       </c>
       <c r="N34" t="b">
         <v>1</v>
@@ -5153,10 +5413,10 @@
         <v>self</v>
       </c>
       <c r="F35">
-        <v>0.12</v>
+        <v>25</v>
       </c>
       <c r="G35">
-        <v>0.03</v>
+        <v>5</v>
       </c>
       <c r="H35">
         <v>6000</v>
@@ -5174,7 +5434,7 @@
         <v>player</v>
       </c>
       <c r="M35" t="str">
-        <v>立即治疗12%，随后3跳各3%。</v>
+        <v>立即固定治疗25点，随后3跳各固定治疗5点。</v>
       </c>
       <c r="N35" t="b">
         <v>1</v>
@@ -5197,7 +5457,7 @@
         <v>self</v>
       </c>
       <c r="F36">
-        <v>0.03</v>
+        <v>5</v>
       </c>
       <c r="G36">
         <v>3</v>
@@ -5218,7 +5478,7 @@
         <v>player</v>
       </c>
       <c r="M36" t="str">
-        <v>周期治疗数据。</v>
+        <v>愈合周期治疗3跳，每跳固定5点。</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -5699,7 +5959,7 @@
         <v>0</v>
       </c>
       <c r="H12" t="str">
-        <v>只对物理伤害生效的叠层减伤。</v>
+        <v>只对物理伤害生效的叠层减伤，每层默认20%，最多3层。</v>
       </c>
       <c r="I12" t="str">
         <v>playerBuff_bearIronfur</v>
@@ -5786,7 +6046,7 @@
         <v>druid_bear_t_barkskin_status_pic</v>
       </c>
       <c r="E15">
-        <v>6000</v>
+        <v>10000</v>
       </c>
       <c r="F15">
         <v>1</v>
@@ -5795,7 +6055,7 @@
         <v>0</v>
       </c>
       <c r="H15" t="str">
-        <v>全伤害减伤。</v>
+        <v>10秒30%全伤害减伤。</v>
       </c>
       <c r="I15" t="str">
         <v>playerBuff_bearBarkskin</v>
@@ -5882,7 +6142,7 @@
         <v>druid_bear_t_incarnation_ursoc_status_pic</v>
       </c>
       <c r="E18">
-        <v>12000</v>
+        <v>30000</v>
       </c>
       <c r="F18">
         <v>1</v>
@@ -5891,7 +6151,7 @@
         <v>0</v>
       </c>
       <c r="H18" t="str">
-        <v>最大生命值和物理减伤。</v>
+        <v>最大生命值提高35%。</v>
       </c>
       <c r="I18" t="str">
         <v>playerBuff_bearIncarnationUrsoc</v>
@@ -5914,7 +6174,7 @@
         <v>druid_bear_t_rage_of_the_sleeper_status_pic</v>
       </c>
       <c r="E19">
-        <v>8000</v>
+        <v>10000</v>
       </c>
       <c r="F19">
         <v>1</v>
@@ -5923,7 +6183,7 @@
         <v>0</v>
       </c>
       <c r="H19" t="str">
-        <v>全伤害减伤和反击。</v>
+        <v>10秒25%全伤害减伤、反击和25%最大生命值提升。</v>
       </c>
       <c r="I19" t="str">
         <v>playerBuff_bearRageOfTheSleeper</v>
@@ -5955,7 +6215,7 @@
         <v>0</v>
       </c>
       <c r="H20" t="str">
-        <v>即时治疗后的周期恢复。</v>
+        <v>即时固定治疗25点后的3跳周期恢复。</v>
       </c>
       <c r="I20" t="str">
         <v>playerBuff_bearRegrowth</v>
@@ -5993,7 +6253,7 @@
         <v>playerBuff_bearIronfurReserve</v>
       </c>
       <c r="J21" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22">
@@ -6025,7 +6285,7 @@
         <v>partyBuff_bearPackPresence</v>
       </c>
       <c r="J22" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23">
@@ -6121,7 +6381,7 @@
         <v>playerBuff_bearWildRecovery</v>
       </c>
       <c r="J25" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26">
@@ -6198,7 +6458,7 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:N37"/>
+  <dimension ref="A1:N38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -6965,7 +7225,7 @@
         <v>2</v>
       </c>
       <c r="F18" t="str">
-        <v>最大生命值提高20%。</v>
+        <v>最大生命值提高30%。</v>
       </c>
       <c r="G18" t="str">
         <v>druid_bear_t_great_bear_vigor_pic</v>
@@ -7009,7 +7269,7 @@
         <v>2</v>
       </c>
       <c r="F19" t="str">
-        <v>常驻8%物理减伤。</v>
+        <v>常驻10%物理减伤，与铁鬃线性叠加。</v>
       </c>
       <c r="G19" t="str">
         <v>druid_bear_t_thick_hide_pic</v>
@@ -7027,7 +7287,7 @@
         <v>2</v>
       </c>
       <c r="L19" t="str">
-        <v/>
+        <v>druid_bear_t_ironfur_choice</v>
       </c>
       <c r="M19" t="str">
         <v/>
@@ -7053,7 +7313,7 @@
         <v>2</v>
       </c>
       <c r="F20" t="str">
-        <v>熊T技能仇恨提高20%。</v>
+        <v>熊T技能额外仇恨提高35%。</v>
       </c>
       <c r="G20" t="str">
         <v>druid_bear_t_ursine_threat_pic</v>
@@ -7097,7 +7357,7 @@
         <v>2</v>
       </c>
       <c r="F21" t="str">
-        <v>裂伤和痛击各额外获得5怒。</v>
+        <v>裂伤额外获得7怒。</v>
       </c>
       <c r="G21" t="str">
         <v>druid_bear_t_savage_focus_pic</v>
@@ -7126,43 +7386,43 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>druid_bear_t_natural_tenacity</v>
+        <v>druid_bear_t_pain_immunity</v>
       </c>
       <c r="B22" t="str">
         <v>druid_bear_t</v>
       </c>
       <c r="C22" t="str">
-        <v>自然坚韧</v>
+        <v>疼痛豁免</v>
       </c>
       <c r="D22" t="str">
-        <v>player</v>
+        <v>skill</v>
       </c>
       <c r="E22">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F22" t="str">
-        <v>控制类减益持续时间缩短25%。</v>
+        <v>痛击不再产生怒气且伤害降低30%；每个命中目标获得5点全伤害吸收，单次最多20点。</v>
       </c>
       <c r="G22" t="str">
-        <v>druid_bear_t_natural_tenacity_pic</v>
+        <v>druid_bear_t_pain_immunity_pic</v>
       </c>
       <c r="H22" t="str">
-        <v>bear_control_duration_reduction</v>
+        <v>bear_pain_immunity</v>
       </c>
       <c r="I22">
         <v>0</v>
       </c>
       <c r="J22" t="str">
-        <v>survival</v>
+        <v>survival,thrash,absorb</v>
       </c>
       <c r="K22">
         <v>5</v>
       </c>
       <c r="L22" t="str">
-        <v/>
+        <v>druid_bear_t_thrash_choice</v>
       </c>
       <c r="M22" t="str">
-        <v/>
+        <v>druid_bear_t_pain_immunity_shield</v>
       </c>
       <c r="N22" t="b">
         <v>1</v>
@@ -7170,40 +7430,40 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>druid_bear_t_ironfur_reserve</v>
+        <v>druid_bear_t_iron_thorns</v>
       </c>
       <c r="B23" t="str">
         <v>druid_bear_t</v>
       </c>
       <c r="C23" t="str">
-        <v>铁鬃余韵</v>
+        <v>铁棘</v>
       </c>
       <c r="D23" t="str">
-        <v>skill</v>
+        <v>party</v>
       </c>
       <c r="E23">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F23" t="str">
-        <v>铁鬃结束后获得3秒8%物理减伤。</v>
+        <v>每层铁鬃使队伍造成的伤害提高15%，最多提高45%。</v>
       </c>
       <c r="G23" t="str">
-        <v>druid_bear_t_ironfur_reserve_pic</v>
+        <v>druid_bear_t_iron_thorns_pic</v>
       </c>
       <c r="H23" t="str">
-        <v>bear_ironfur_reserve</v>
+        <v>bear_iron_thorns</v>
       </c>
       <c r="I23">
         <v>1</v>
       </c>
       <c r="J23" t="str">
-        <v>survival</v>
+        <v>party,damage,ironfur</v>
       </c>
       <c r="K23">
         <v>6</v>
       </c>
       <c r="L23" t="str">
-        <v/>
+        <v>druid_bear_t_party_offense</v>
       </c>
       <c r="M23" t="str">
         <v/>
@@ -7214,40 +7474,40 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>druid_bear_t_blood_scent</v>
+        <v>druid_bear_t_natural_inspiration</v>
       </c>
       <c r="B24" t="str">
         <v>druid_bear_t</v>
       </c>
       <c r="C24" t="str">
-        <v>血性气息</v>
+        <v>自然鼓舞</v>
       </c>
       <c r="D24" t="str">
-        <v>skill</v>
+        <v>party</v>
       </c>
       <c r="E24">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F24" t="str">
-        <v>狂暴回复期间首次受伤获得8怒。</v>
+        <v>队伍自动攻击间隔缩短25%。</v>
       </c>
       <c r="G24" t="str">
-        <v>druid_bear_t_blood_scent_pic</v>
+        <v>druid_bear_t_natural_inspiration_pic</v>
       </c>
       <c r="H24" t="str">
-        <v>bear_blood_scent</v>
+        <v>bear_natural_inspiration</v>
       </c>
       <c r="I24">
         <v>1</v>
       </c>
       <c r="J24" t="str">
-        <v>survival</v>
+        <v>party,damage,auto-attack</v>
       </c>
       <c r="K24">
         <v>7</v>
       </c>
       <c r="L24" t="str">
-        <v/>
+        <v>druid_bear_t_party_offense</v>
       </c>
       <c r="M24" t="str">
         <v/>
@@ -7273,7 +7533,7 @@
         <v>2</v>
       </c>
       <c r="F25" t="str">
-        <v>成功打断获得10怒。</v>
+        <v>成功打断获得15怒气。</v>
       </c>
       <c r="G25" t="str">
         <v>druid_bear_t_skull_bash_instinct_pic</v>
@@ -7317,7 +7577,7 @@
         <v>2</v>
       </c>
       <c r="F26" t="str">
-        <v>吸收盾提前破碎获得12怒。</v>
+        <v>树皮术额外消耗10点怒气并获得5秒30点全伤害吸收护盾；护盾提前耗尽时获得30点怒气。</v>
       </c>
       <c r="G26" t="str">
         <v>druid_bear_t_broken_bark_pic</v>
@@ -7338,7 +7598,7 @@
         <v/>
       </c>
       <c r="M26" t="str">
-        <v/>
+        <v>druid_bear_t_broken_bark_shield</v>
       </c>
       <c r="N26" t="b">
         <v>1</v>
@@ -7346,13 +7606,13 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>druid_bear_t_pack_presence</v>
+        <v>druid_bear_t_mark_of_the_wild</v>
       </c>
       <c r="B27" t="str">
         <v>druid_bear_t</v>
       </c>
       <c r="C27" t="str">
-        <v>兽群威势</v>
+        <v>野性印记</v>
       </c>
       <c r="D27" t="str">
         <v>party</v>
@@ -7361,25 +7621,25 @@
         <v>3</v>
       </c>
       <c r="F27" t="str">
-        <v>铁鬃两层时队伍获得8%全伤害减伤。</v>
+        <v>熊T自身和队伍造成的伤害提高25%。</v>
       </c>
       <c r="G27" t="str">
-        <v>druid_bear_t_pack_presence_pic</v>
+        <v>druid_bear_t_mark_of_the_wild_pic</v>
       </c>
       <c r="H27" t="str">
-        <v>bear_pack_presence</v>
+        <v>bear_mark_of_the_wild</v>
       </c>
       <c r="I27">
         <v>1</v>
       </c>
       <c r="J27" t="str">
-        <v>party,survival</v>
+        <v>party,damage,player</v>
       </c>
       <c r="K27">
         <v>10</v>
       </c>
       <c r="L27" t="str">
-        <v/>
+        <v>druid_bear_t_party_offense</v>
       </c>
       <c r="M27" t="str">
         <v/>
@@ -7405,7 +7665,7 @@
         <v>2</v>
       </c>
       <c r="F28" t="str">
-        <v>月火术存在时熊T获得5%全伤害减伤。</v>
+        <v>月火术存在时熊T获得10%全伤害减免。</v>
       </c>
       <c r="G28" t="str">
         <v>druid_bear_t_moonlit_resolve_pic</v>
@@ -7449,7 +7709,7 @@
         <v>2</v>
       </c>
       <c r="F29" t="str">
-        <v>树皮术结束时解除所有可驱散玩家减益。</v>
+        <v>树皮术结束时解除所有可驱散玩家减益，并治疗当前最大生命值的10%。</v>
       </c>
       <c r="G29" t="str">
         <v>druid_bear_t_bark_dispelling_pic</v>
@@ -7490,7 +7750,7 @@
         <v>party</v>
       </c>
       <c r="E30">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="F30" t="str">
         <v>狂暴回复最后一跳治疗队伍5点。</v>
@@ -7566,40 +7826,40 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>druid_bear_t_wild_recovery</v>
+        <v>druid_bear_t_water_fire_immunity</v>
       </c>
       <c r="B32" t="str">
         <v>druid_bear_t</v>
       </c>
       <c r="C32" t="str">
-        <v>野性复原</v>
+        <v>水火不侵</v>
       </c>
       <c r="D32" t="str">
         <v>player</v>
       </c>
       <c r="E32">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F32" t="str">
-        <v>有效治疗后获得短时最大生命值提升。</v>
+        <v>铁鬃每层获得20%物理伤害减免和10%魔法伤害减免，最多3层。</v>
       </c>
       <c r="G32" t="str">
-        <v>druid_bear_t_wild_recovery_pic</v>
+        <v>druid_bear_t_water_fire_immunity_pic</v>
       </c>
       <c r="H32" t="str">
-        <v>bear_wild_recovery</v>
+        <v>bear_water_fire_immunity</v>
       </c>
       <c r="I32">
         <v>2</v>
       </c>
       <c r="J32" t="str">
-        <v>survival</v>
+        <v>survival,ironfur,magic</v>
       </c>
       <c r="K32">
         <v>15</v>
       </c>
       <c r="L32" t="str">
-        <v/>
+        <v>druid_bear_t_ironfur_choice</v>
       </c>
       <c r="M32" t="str">
         <v/>
@@ -7625,7 +7885,7 @@
         <v>3</v>
       </c>
       <c r="F33" t="str">
-        <v>愈合同时治疗队伍原始治疗量25%。</v>
+        <v>愈合同时治疗队伍原始即时治疗量的50%；持续治疗不治疗队伍。</v>
       </c>
       <c r="G33" t="str">
         <v>druid_bear_t_regrowth_of_the_pack_pic</v>
@@ -7669,7 +7929,7 @@
         <v>3</v>
       </c>
       <c r="F34" t="str">
-        <v>熊T高于80%生命时队伍获得6%全伤害减伤。</v>
+        <v>熊T高于80%生命时队伍获得25%全伤害减伤。</v>
       </c>
       <c r="G34" t="str">
         <v>druid_bear_t_guardian_of_the_grove_pic</v>
@@ -7757,7 +8017,7 @@
         <v>4</v>
       </c>
       <c r="F36" t="str">
-        <v>每场战斗一次致命伤害保留1生命并获得铁鬃。</v>
+        <v>每场战斗一次，致命伤害后保留15%最大生命并在10秒内无法获得怒气。</v>
       </c>
       <c r="G36" t="str">
         <v>druid_bear_t_last_bear_stand_pic</v>
@@ -7778,7 +8038,7 @@
         <v/>
       </c>
       <c r="M36" t="str">
-        <v/>
+        <v>druid_bear_t_rage_exhaustion</v>
       </c>
       <c r="N36" t="b">
         <v>1</v>
@@ -7801,7 +8061,7 @@
         <v>3</v>
       </c>
       <c r="F37" t="str">
-        <v>每累计获得30怒治疗队伍5点生命。</v>
+        <v>每累计获得60怒治疗队伍5点生命。</v>
       </c>
       <c r="G37" t="str">
         <v>druid_bear_t_spring_returns_pic</v>
@@ -7825,20 +8085,64 @@
         <v/>
       </c>
       <c r="N37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>druid_bear_t_pain_rage</v>
+      </c>
+      <c r="B38" t="str">
+        <v>druid_bear_t</v>
+      </c>
+      <c r="C38" t="str">
+        <v>痛苦之怒</v>
+      </c>
+      <c r="D38" t="str">
+        <v>skill</v>
+      </c>
+      <c r="E38">
+        <v>4</v>
+      </c>
+      <c r="F38" t="str">
+        <v>痛击每命中一个敌人额外获得2怒，单次最多额外获得10怒。</v>
+      </c>
+      <c r="G38" t="str">
+        <v>druid_bear_t_pain_rage_pic</v>
+      </c>
+      <c r="H38" t="str">
+        <v>bear_pain_rage</v>
+      </c>
+      <c r="I38">
+        <v>0</v>
+      </c>
+      <c r="J38" t="str">
+        <v>rage,aoe</v>
+      </c>
+      <c r="K38">
+        <v>21</v>
+      </c>
+      <c r="L38" t="str">
+        <v>druid_bear_t_thrash_choice</v>
+      </c>
+      <c r="M38" t="str">
+        <v/>
+      </c>
+      <c r="N38" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:N37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:N38"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:K37"/>
+  <dimension ref="A1:K38"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -8452,7 +8756,7 @@
         <v>player</v>
       </c>
       <c r="F18">
-        <v>0.2</v>
+        <v>0.3</v>
       </c>
       <c r="G18">
         <v>0</v>
@@ -8464,7 +8768,7 @@
         <v/>
       </c>
       <c r="J18" t="str">
-        <v>最大生命值提高20%。</v>
+        <v>最大生命值提高30%。</v>
       </c>
       <c r="K18" t="b">
         <v>1</v>
@@ -8487,7 +8791,7 @@
         <v>player</v>
       </c>
       <c r="F19">
-        <v>0.08</v>
+        <v>0.1</v>
       </c>
       <c r="G19">
         <v>0</v>
@@ -8499,7 +8803,7 @@
         <v/>
       </c>
       <c r="J19" t="str">
-        <v>常驻8%物理减伤。</v>
+        <v>常驻10%物理减伤，与铁鬃线性叠加。</v>
       </c>
       <c r="K19" t="b">
         <v>1</v>
@@ -8522,7 +8826,7 @@
         <v>skill</v>
       </c>
       <c r="F20">
-        <v>0.2</v>
+        <v>0.35</v>
       </c>
       <c r="G20">
         <v>0</v>
@@ -8534,7 +8838,7 @@
         <v/>
       </c>
       <c r="J20" t="str">
-        <v>熊T技能仇恨提高20%。</v>
+        <v>熊T技能额外仇恨提高35%。</v>
       </c>
       <c r="K20" t="b">
         <v>1</v>
@@ -8557,7 +8861,7 @@
         <v>player</v>
       </c>
       <c r="F21">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="G21">
         <v>0</v>
@@ -8569,7 +8873,7 @@
         <v/>
       </c>
       <c r="J21" t="str">
-        <v>裂伤和痛击各额外获得5怒。</v>
+        <v>裂伤额外获得7怒。</v>
       </c>
       <c r="K21" t="b">
         <v>1</v>
@@ -8577,34 +8881,34 @@
     </row>
     <row r="22">
       <c r="A22" t="str">
-        <v>druid_bear_t_natural_tenacity_main</v>
+        <v>druid_bear_t_pain_immunity_main</v>
       </c>
       <c r="B22" t="str">
-        <v>druid_bear_t_natural_tenacity</v>
+        <v>druid_bear_t_pain_immunity</v>
       </c>
       <c r="C22">
         <v>1</v>
       </c>
       <c r="D22" t="str">
-        <v>bear_control_duration_reduction</v>
+        <v>bear_pain_immunity</v>
       </c>
       <c r="E22" t="str">
-        <v>player</v>
+        <v>skill</v>
       </c>
       <c r="F22">
-        <v>0.25</v>
+        <v>5</v>
       </c>
       <c r="G22">
-        <v>0</v>
+        <v>20</v>
       </c>
       <c r="H22" t="str">
-        <v/>
+        <v>druid_bear_t_pain_immunity_shield</v>
       </c>
       <c r="I22" t="str">
-        <v/>
+        <v>druid_bear_t_thrash</v>
       </c>
       <c r="J22" t="str">
-        <v>控制类减益持续时间缩短25%。</v>
+        <v>痛击不再产生怒气且伤害降低30%；每个命中目标获得5点全伤害吸收，单次最多20点。</v>
       </c>
       <c r="K22" t="b">
         <v>1</v>
@@ -8612,25 +8916,25 @@
     </row>
     <row r="23">
       <c r="A23" t="str">
-        <v>druid_bear_t_ironfur_reserve_main</v>
+        <v>druid_bear_t_iron_thorns_main</v>
       </c>
       <c r="B23" t="str">
-        <v>druid_bear_t_ironfur_reserve</v>
+        <v>druid_bear_t_iron_thorns</v>
       </c>
       <c r="C23">
         <v>1</v>
       </c>
       <c r="D23" t="str">
-        <v>bear_ironfur_reserve</v>
+        <v>bear_iron_thorns</v>
       </c>
       <c r="E23" t="str">
-        <v>skill</v>
+        <v>party</v>
       </c>
       <c r="F23">
-        <v>0.08</v>
+        <v>0.15</v>
       </c>
       <c r="G23">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="str">
         <v/>
@@ -8639,7 +8943,7 @@
         <v/>
       </c>
       <c r="J23" t="str">
-        <v>铁鬃结束后获得3秒8%物理减伤。</v>
+        <v>每层铁鬃使队伍造成的伤害提高15%，最多提高45%。</v>
       </c>
       <c r="K23" t="b">
         <v>1</v>
@@ -8647,22 +8951,22 @@
     </row>
     <row r="24">
       <c r="A24" t="str">
-        <v>druid_bear_t_blood_scent_main</v>
+        <v>druid_bear_t_natural_inspiration_main</v>
       </c>
       <c r="B24" t="str">
-        <v>druid_bear_t_blood_scent</v>
+        <v>druid_bear_t_natural_inspiration</v>
       </c>
       <c r="C24">
         <v>1</v>
       </c>
       <c r="D24" t="str">
-        <v>bear_blood_scent</v>
+        <v>bear_natural_inspiration</v>
       </c>
       <c r="E24" t="str">
-        <v>skill</v>
+        <v>party</v>
       </c>
       <c r="F24">
-        <v>8</v>
+        <v>0.25</v>
       </c>
       <c r="G24">
         <v>0</v>
@@ -8674,7 +8978,7 @@
         <v/>
       </c>
       <c r="J24" t="str">
-        <v>狂暴回复期间首次受伤获得8怒。</v>
+        <v>队伍自动攻击间隔缩短25%。</v>
       </c>
       <c r="K24" t="b">
         <v>1</v>
@@ -8697,7 +9001,7 @@
         <v>skill</v>
       </c>
       <c r="F25">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="G25">
         <v>0</v>
@@ -8709,7 +9013,7 @@
         <v>druid_bear_t_skull_bash</v>
       </c>
       <c r="J25" t="str">
-        <v>成功打断获得10怒。</v>
+        <v>成功打断获得15怒气。</v>
       </c>
       <c r="K25" t="b">
         <v>1</v>
@@ -8732,19 +9036,19 @@
         <v>skill</v>
       </c>
       <c r="F26">
-        <v>12</v>
+        <v>30</v>
       </c>
       <c r="G26">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H26" t="str">
-        <v/>
+        <v>druid_bear_t_broken_bark_shield</v>
       </c>
       <c r="I26" t="str">
-        <v/>
+        <v>druid_bear_t_barkskin</v>
       </c>
       <c r="J26" t="str">
-        <v>吸收盾提前破碎获得12怒。</v>
+        <v>树皮术额外消耗10怒并获得5秒30点全伤害吸收护盾；护盾提前耗尽返还30怒。</v>
       </c>
       <c r="K26" t="b">
         <v>1</v>
@@ -8752,34 +9056,34 @@
     </row>
     <row r="27">
       <c r="A27" t="str">
-        <v>druid_bear_t_pack_presence_main</v>
+        <v>druid_bear_t_mark_of_the_wild_main</v>
       </c>
       <c r="B27" t="str">
-        <v>druid_bear_t_pack_presence</v>
+        <v>druid_bear_t_mark_of_the_wild</v>
       </c>
       <c r="C27">
         <v>1</v>
       </c>
       <c r="D27" t="str">
-        <v>bear_pack_presence</v>
+        <v>bear_mark_of_the_wild</v>
       </c>
       <c r="E27" t="str">
-        <v>party</v>
+        <v>player</v>
       </c>
       <c r="F27">
-        <v>0.08</v>
+        <v>0.25</v>
       </c>
       <c r="G27">
         <v>0</v>
       </c>
       <c r="H27" t="str">
-        <v>druid_bear_t_pack_presence</v>
+        <v/>
       </c>
       <c r="I27" t="str">
         <v/>
       </c>
       <c r="J27" t="str">
-        <v>铁鬃两层时队伍获得8%全伤害减伤。</v>
+        <v>熊T自身和队伍造成的伤害提高25%。</v>
       </c>
       <c r="K27" t="b">
         <v>1</v>
@@ -8802,7 +9106,7 @@
         <v>skill</v>
       </c>
       <c r="F28">
-        <v>0.05</v>
+        <v>0.1</v>
       </c>
       <c r="G28">
         <v>0</v>
@@ -8814,7 +9118,7 @@
         <v>druid_bear_t_moonfire</v>
       </c>
       <c r="J28" t="str">
-        <v>月火术存在时熊T获得5%全伤害减伤。</v>
+        <v>月火术存在时熊T获得10%全伤害减免。</v>
       </c>
       <c r="K28" t="b">
         <v>1</v>
@@ -8837,7 +9141,7 @@
         <v>skill</v>
       </c>
       <c r="F29">
-        <v>0</v>
+        <v>0.1</v>
       </c>
       <c r="G29">
         <v>0</v>
@@ -8849,7 +9153,7 @@
         <v>druid_bear_t_barkskin</v>
       </c>
       <c r="J29" t="str">
-        <v>树皮术结束时解除所有可驱散玩家减益。</v>
+        <v>树皮术结束时解除所有可驱散玩家减益，并治疗当前最大生命值的10%。</v>
       </c>
       <c r="K29" t="b">
         <v>1</v>
@@ -8927,34 +9231,34 @@
     </row>
     <row r="32">
       <c r="A32" t="str">
-        <v>druid_bear_t_wild_recovery_main</v>
+        <v>druid_bear_t_water_fire_immunity_main</v>
       </c>
       <c r="B32" t="str">
-        <v>druid_bear_t_wild_recovery</v>
+        <v>druid_bear_t_water_fire_immunity</v>
       </c>
       <c r="C32">
         <v>1</v>
       </c>
       <c r="D32" t="str">
-        <v>bear_wild_recovery</v>
+        <v>bear_water_fire_immunity</v>
       </c>
       <c r="E32" t="str">
         <v>player</v>
       </c>
       <c r="F32">
+        <v>0.2</v>
+      </c>
+      <c r="G32">
         <v>0.1</v>
       </c>
-      <c r="G32">
-        <v>10</v>
-      </c>
       <c r="H32" t="str">
-        <v>druid_bear_t_wild_recovery</v>
+        <v/>
       </c>
       <c r="I32" t="str">
-        <v/>
+        <v>druid_bear_t_ironfur</v>
       </c>
       <c r="J32" t="str">
-        <v>有效治疗后获得短时最大生命值提升。</v>
+        <v>铁鬃每层获得20%物理伤害减免和10%魔法伤害减免，最多3层。</v>
       </c>
       <c r="K32" t="b">
         <v>1</v>
@@ -8977,7 +9281,7 @@
         <v>party</v>
       </c>
       <c r="F33">
-        <v>0.25</v>
+        <v>0.5</v>
       </c>
       <c r="G33">
         <v>0</v>
@@ -8989,7 +9293,7 @@
         <v>druid_bear_t_regrowth</v>
       </c>
       <c r="J33" t="str">
-        <v>愈合同时治疗队伍原始治疗量25%。</v>
+        <v>愈合同时治疗队伍原始即时治疗量的50%；持续治疗不治疗队伍。</v>
       </c>
       <c r="K33" t="b">
         <v>1</v>
@@ -9012,7 +9316,7 @@
         <v>party</v>
       </c>
       <c r="F34">
-        <v>0.06</v>
+        <v>0.25</v>
       </c>
       <c r="G34">
         <v>0.8</v>
@@ -9024,7 +9328,7 @@
         <v/>
       </c>
       <c r="J34" t="str">
-        <v>熊T高于80%生命时队伍获得6%全伤害减伤。</v>
+        <v>熊T高于80%生命时队伍获得25%全伤害减伤。</v>
       </c>
       <c r="K34" t="b">
         <v>1</v>
@@ -9082,19 +9386,19 @@
         <v>player</v>
       </c>
       <c r="F36">
-        <v>1</v>
+        <v>0.15</v>
       </c>
       <c r="G36">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="H36" t="str">
-        <v/>
+        <v>druid_bear_t_rage_exhaustion</v>
       </c>
       <c r="I36" t="str">
         <v/>
       </c>
       <c r="J36" t="str">
-        <v>每场战斗一次致命伤害保留1生命并获得铁鬃。</v>
+        <v>致命伤害后保留15%最大生命，并施加10秒可驱散禁怒减益。</v>
       </c>
       <c r="K36" t="b">
         <v>1</v>
@@ -9117,7 +9421,7 @@
         <v>party</v>
       </c>
       <c r="F37">
-        <v>30</v>
+        <v>60</v>
       </c>
       <c r="G37">
         <v>5</v>
@@ -9129,23 +9433,58 @@
         <v/>
       </c>
       <c r="J37" t="str">
-        <v>每累计获得30怒治疗队伍5点生命。</v>
+        <v>每累计获得60怒治疗队伍5点生命。</v>
       </c>
       <c r="K37" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="str">
+        <v>druid_bear_t_pain_rage_main</v>
+      </c>
+      <c r="B38" t="str">
+        <v>druid_bear_t_pain_rage</v>
+      </c>
+      <c r="C38">
+        <v>1</v>
+      </c>
+      <c r="D38" t="str">
+        <v>bear_pain_rage</v>
+      </c>
+      <c r="E38" t="str">
+        <v>skill</v>
+      </c>
+      <c r="F38">
+        <v>2</v>
+      </c>
+      <c r="G38">
+        <v>10</v>
+      </c>
+      <c r="H38" t="str">
+        <v/>
+      </c>
+      <c r="I38" t="str">
+        <v>druid_bear_t_thrash</v>
+      </c>
+      <c r="J38" t="str">
+        <v>痛击每命中一个敌人额外获得2怒，单次最多10怒。</v>
+      </c>
+      <c r="K38" t="b">
         <v>1</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:K37"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:K38"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:J15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -9368,7 +9707,7 @@
         <v>partyBuff_bearPackPresence</v>
       </c>
       <c r="J7" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -9464,7 +9803,7 @@
         <v>playerBuff_bearWildRecovery</v>
       </c>
       <c r="J10" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11">
@@ -9531,17 +9870,113 @@
         <v>1</v>
       </c>
     </row>
+    <row r="13">
+      <c r="A13" t="str">
+        <v>druid_bear_t_broken_bark_shield</v>
+      </c>
+      <c r="B13" t="str">
+        <v>破盾树皮</v>
+      </c>
+      <c r="C13" t="str">
+        <v>playerBuff</v>
+      </c>
+      <c r="D13" t="str">
+        <v>druid_bear_t_broken_bark_pic</v>
+      </c>
+      <c r="E13">
+        <v>5000</v>
+      </c>
+      <c r="F13">
+        <v>1</v>
+      </c>
+      <c r="G13" t="b">
+        <v>0</v>
+      </c>
+      <c r="H13" t="str">
+        <v>吸收30点全伤害；持续时间结束前完全破碎时返还30点怒气。</v>
+      </c>
+      <c r="I13" t="str">
+        <v>bear_broken_bark_shield</v>
+      </c>
+      <c r="J13" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="str">
+        <v>druid_bear_t_rage_exhaustion</v>
+      </c>
+      <c r="B14" t="str">
+        <v>怒气枯竭</v>
+      </c>
+      <c r="C14" t="str">
+        <v>enemyDebuff</v>
+      </c>
+      <c r="D14" t="str">
+        <v>druid_bear_t_rage_exhaustion_pic</v>
+      </c>
+      <c r="E14">
+        <v>10000</v>
+      </c>
+      <c r="F14">
+        <v>1</v>
+      </c>
+      <c r="G14" t="b">
+        <v>1</v>
+      </c>
+      <c r="H14" t="str">
+        <v>无法获得任何怒气。</v>
+      </c>
+      <c r="I14" t="str">
+        <v>bear_rage_exhaustion</v>
+      </c>
+      <c r="J14" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="str">
+        <v>druid_bear_t_pain_immunity_shield</v>
+      </c>
+      <c r="B15" t="str">
+        <v>疼痛豁免护盾</v>
+      </c>
+      <c r="C15" t="str">
+        <v>playerBuff</v>
+      </c>
+      <c r="D15" t="str">
+        <v>druid_bear_t_pain_immunity_status_pic</v>
+      </c>
+      <c r="E15">
+        <v>9000</v>
+      </c>
+      <c r="F15">
+        <v>1</v>
+      </c>
+      <c r="G15" t="b">
+        <v>0</v>
+      </c>
+      <c r="H15" t="str">
+        <v>疼痛豁免由痛击命中产生的全伤害吸收护盾。</v>
+      </c>
+      <c r="I15" t="str">
+        <v>playerBuff_bearPainImmunity</v>
+      </c>
+      <c r="J15" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:J12"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:J15"/>
   </ignoredErrors>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:E102"/>
+  <dimension ref="A1:E105"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="str">
@@ -10735,10 +11170,10 @@
     </row>
     <row r="71">
       <c r="A71" t="str">
-        <v>druid_bear_t_natural_tenacity_pic</v>
+        <v>druid_bear_t_pain_immunity_pic</v>
       </c>
       <c r="B71" t="str">
-        <v>自然坚韧</v>
+        <v>疼痛豁免</v>
       </c>
       <c r="C71" t="str">
         <v>bear-leaf</v>
@@ -10752,10 +11187,10 @@
     </row>
     <row r="72">
       <c r="A72" t="str">
-        <v>druid_bear_t_ironfur_reserve_pic</v>
+        <v>druid_bear_t_iron_thorns_pic</v>
       </c>
       <c r="B72" t="str">
-        <v>铁鬃余韵</v>
+        <v>铁棘</v>
       </c>
       <c r="C72" t="str">
         <v>bear-leaf</v>
@@ -10769,10 +11204,10 @@
     </row>
     <row r="73">
       <c r="A73" t="str">
-        <v>druid_bear_t_blood_scent_pic</v>
+        <v>druid_bear_t_natural_inspiration_pic</v>
       </c>
       <c r="B73" t="str">
-        <v>血性气息</v>
+        <v>自然鼓舞</v>
       </c>
       <c r="C73" t="str">
         <v>bear-leaf</v>
@@ -10820,10 +11255,10 @@
     </row>
     <row r="76">
       <c r="A76" t="str">
-        <v>druid_bear_t_pack_presence_pic</v>
+        <v>druid_bear_t_mark_of_the_wild_pic</v>
       </c>
       <c r="B76" t="str">
-        <v>兽群威势</v>
+        <v>野性印记</v>
       </c>
       <c r="C76" t="str">
         <v>bear-leaf</v>
@@ -10905,10 +11340,10 @@
     </row>
     <row r="81">
       <c r="A81" t="str">
-        <v>druid_bear_t_wild_recovery_pic</v>
+        <v>druid_bear_t_water_fire_immunity_pic</v>
       </c>
       <c r="B81" t="str">
-        <v>野性复原</v>
+        <v>水火不侵</v>
       </c>
       <c r="C81" t="str">
         <v>bear-leaf</v>
@@ -11172,7 +11607,7 @@
         <v>status</v>
       </c>
       <c r="E96" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97">
@@ -11189,7 +11624,7 @@
         <v>status</v>
       </c>
       <c r="E97" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98">
@@ -11277,10 +11712,61 @@
         <v>1</v>
       </c>
     </row>
+    <row r="103">
+      <c r="A103" t="str">
+        <v>druid_bear_t_pain_rage_pic</v>
+      </c>
+      <c r="B103" t="str">
+        <v>痛苦之怒</v>
+      </c>
+      <c r="C103" t="str">
+        <v>bear-pain-rage</v>
+      </c>
+      <c r="D103" t="str">
+        <v>talent</v>
+      </c>
+      <c r="E103" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="str">
+        <v>druid_bear_t_rage_exhaustion_pic</v>
+      </c>
+      <c r="B104" t="str">
+        <v>怒气枯竭</v>
+      </c>
+      <c r="C104" t="str">
+        <v>bear-rage-lock</v>
+      </c>
+      <c r="D104" t="str">
+        <v>status</v>
+      </c>
+      <c r="E104" t="b">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="str">
+        <v>druid_bear_t_pain_immunity_status_pic</v>
+      </c>
+      <c r="B105" t="str">
+        <v>疼痛豁免护盾</v>
+      </c>
+      <c r="C105" t="str">
+        <v>bear-aura</v>
+      </c>
+      <c r="D105" t="str">
+        <v>status</v>
+      </c>
+      <c r="E105" t="b">
+        <v>1</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <ignoredErrors>
-    <ignoredError numberStoredAsText="1" sqref="A1:E102"/>
+    <ignoredError numberStoredAsText="1" sqref="A1:E105"/>
   </ignoredErrors>
 </worksheet>
 </file>
--- a/public/designer-data/player_build.xlsx
+++ b/public/designer-data/player_build.xlsx
@@ -131,10 +131,10 @@
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -166,10 +166,10 @@
         <a:latin typeface="Calibri"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="ÃÂ¯ÃÂ¼ÃÂ­ÃÂ¯ÃÂ¼ÃÂ³ ÃÂ¯ÃÂ¼ÃÂ°ÃÂ£ÃÂÃÂ´ÃÂ£ÃÂÃÂ·ÃÂ£ÃÂÃÂÃÂ£ÃÂÃÂ¯"/>
-        <a:font script="Hang" typeface="ÃÂ«ÃÂ§ÃÂÃÂ¬ÃÂÃÂ ÃÂªÃÂ³ÃÂ ÃÂ«ÃÂÃÂ"/>
-        <a:font script="Hans" typeface="ÃÂ¥ÃÂ®ÃÂÃÂ¤ÃÂ½ÃÂ"/>
-        <a:font script="Hant" typeface="ÃÂ¦ÃÂÃÂ°ÃÂ§ÃÂ´ÃÂ°ÃÂ¦ÃÂÃÂÃÂ©ÃÂ«ÃÂ"/>
+        <a:font script="Jpan" typeface="ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ­ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ³ ÃÂÃÂ¯ÃÂÃÂ¼ÃÂÃÂ°ÃÂÃÂ£ÃÂÃÂÃÂÃÂ´ÃÂÃÂ£ÃÂÃÂÃÂÃÂ·ÃÂÃÂ£ÃÂÃÂÃÂÃÂÃÂÃÂ£ÃÂÃÂÃÂÃÂ¯"/>
+        <a:font script="Hang" typeface="ÃÂÃÂ«ÃÂÃÂ§ÃÂÃÂÃÂÃÂ¬ÃÂÃÂÃÂÃÂ ÃÂÃÂªÃÂÃÂ³ÃÂÃÂ ÃÂÃÂ«ÃÂÃÂÃÂÃÂ"/>
+        <a:font script="Hans" typeface="ÃÂÃÂ¥ÃÂÃÂ®ÃÂÃÂÃÂÃÂ¤ÃÂÃÂ½ÃÂÃÂ"/>
+        <a:font script="Hant" typeface="ÃÂÃÂ¦ÃÂÃÂÃÂÃÂ°ÃÂÃÂ§ÃÂÃÂ´ÃÂÃÂ°ÃÂÃÂ¦ÃÂÃÂÃÂÃÂÃÂÃÂ©ÃÂÃÂ«ÃÂÃÂ"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
         <a:font script="Thai" typeface="Tahoma"/>
@@ -10836,7 +10836,7 @@
         <v>低吼</v>
       </c>
       <c r="C51" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-growl</v>
       </c>
       <c r="D51" t="str">
         <v>skill</v>
@@ -10853,7 +10853,7 @@
         <v>裂伤</v>
       </c>
       <c r="C52" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-mangle</v>
       </c>
       <c r="D52" t="str">
         <v>skill</v>
@@ -10870,7 +10870,7 @@
         <v>痛击</v>
       </c>
       <c r="C53" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-thrash</v>
       </c>
       <c r="D53" t="str">
         <v>skill</v>
@@ -10887,7 +10887,7 @@
         <v>迎头痛击</v>
       </c>
       <c r="C54" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-skull-bash</v>
       </c>
       <c r="D54" t="str">
         <v>skill</v>
@@ -10904,7 +10904,7 @@
         <v>铁鬃</v>
       </c>
       <c r="C55" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-ironfur</v>
       </c>
       <c r="D55" t="str">
         <v>skill</v>
@@ -10921,7 +10921,7 @@
         <v>狂暴回复</v>
       </c>
       <c r="C56" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-frenzied-regeneration</v>
       </c>
       <c r="D56" t="str">
         <v>skill</v>
@@ -10938,7 +10938,7 @@
         <v>横扫</v>
       </c>
       <c r="C57" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-swipe</v>
       </c>
       <c r="D57" t="str">
         <v>skill</v>
@@ -10955,7 +10955,7 @@
         <v>月火术</v>
       </c>
       <c r="C58" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-moonfire</v>
       </c>
       <c r="D58" t="str">
         <v>skill</v>
@@ -10972,7 +10972,7 @@
         <v>树皮术</v>
       </c>
       <c r="C59" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-barkskin</v>
       </c>
       <c r="D59" t="str">
         <v>skill</v>
@@ -10989,7 +10989,7 @@
         <v>生存本能</v>
       </c>
       <c r="C60" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-survival-instincts</v>
       </c>
       <c r="D60" t="str">
         <v>skill</v>
@@ -11006,7 +11006,7 @@
         <v>明月普照</v>
       </c>
       <c r="C61" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-lunar-beam</v>
       </c>
       <c r="D61" t="str">
         <v>skill</v>
@@ -11023,7 +11023,7 @@
         <v>乌索克的化身</v>
       </c>
       <c r="C62" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-incarnation-ursoc</v>
       </c>
       <c r="D62" t="str">
         <v>skill</v>
@@ -11040,7 +11040,7 @@
         <v>沉睡者之怒</v>
       </c>
       <c r="C63" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-rage-of-the-sleeper</v>
       </c>
       <c r="D63" t="str">
         <v>skill</v>
@@ -11057,7 +11057,7 @@
         <v>愈合</v>
       </c>
       <c r="C64" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-regrowth</v>
       </c>
       <c r="D64" t="str">
         <v>skill</v>
@@ -11074,7 +11074,7 @@
         <v>狂暴</v>
       </c>
       <c r="C65" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-berserk</v>
       </c>
       <c r="D65" t="str">
         <v>skill</v>
@@ -11091,7 +11091,7 @@
         <v>咆哮</v>
       </c>
       <c r="C66" t="str">
-        <v>bear-claw</v>
+        <v>bear-skill-roar</v>
       </c>
       <c r="D66" t="str">
         <v>skill</v>
@@ -11108,7 +11108,7 @@
         <v>巨熊活力</v>
       </c>
       <c r="C67" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-great-bear-vigor</v>
       </c>
       <c r="D67" t="str">
         <v>talent</v>
@@ -11125,7 +11125,7 @@
         <v>厚皮</v>
       </c>
       <c r="C68" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-thick-hide</v>
       </c>
       <c r="D68" t="str">
         <v>talent</v>
@@ -11142,7 +11142,7 @@
         <v>熊威</v>
       </c>
       <c r="C69" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-ursine-threat</v>
       </c>
       <c r="D69" t="str">
         <v>talent</v>
@@ -11159,7 +11159,7 @@
         <v>野性专注</v>
       </c>
       <c r="C70" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-savage-focus</v>
       </c>
       <c r="D70" t="str">
         <v>talent</v>
@@ -11176,7 +11176,7 @@
         <v>疼痛豁免</v>
       </c>
       <c r="C71" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-pain-immunity</v>
       </c>
       <c r="D71" t="str">
         <v>talent</v>
@@ -11193,7 +11193,7 @@
         <v>铁棘</v>
       </c>
       <c r="C72" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-iron-thorns</v>
       </c>
       <c r="D72" t="str">
         <v>talent</v>
@@ -11210,7 +11210,7 @@
         <v>自然鼓舞</v>
       </c>
       <c r="C73" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-natural-inspiration</v>
       </c>
       <c r="D73" t="str">
         <v>talent</v>
@@ -11227,7 +11227,7 @@
         <v>断法本能</v>
       </c>
       <c r="C74" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-skull-bash-instinct</v>
       </c>
       <c r="D74" t="str">
         <v>talent</v>
@@ -11244,7 +11244,7 @@
         <v>破盾回响</v>
       </c>
       <c r="C75" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-broken-bark</v>
       </c>
       <c r="D75" t="str">
         <v>talent</v>
@@ -11261,7 +11261,7 @@
         <v>野性印记</v>
       </c>
       <c r="C76" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-mark-of-the-wild</v>
       </c>
       <c r="D76" t="str">
         <v>talent</v>
@@ -11278,7 +11278,7 @@
         <v>月下坚守</v>
       </c>
       <c r="C77" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-moonlit-resolve</v>
       </c>
       <c r="D77" t="str">
         <v>talent</v>
@@ -11295,7 +11295,7 @@
         <v>树皮净化</v>
       </c>
       <c r="C78" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-bark-dispelling</v>
       </c>
       <c r="D78" t="str">
         <v>talent</v>
@@ -11312,7 +11312,7 @@
         <v>回春羁绊</v>
       </c>
       <c r="C79" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-regenerative-bond</v>
       </c>
       <c r="D79" t="str">
         <v>talent</v>
@@ -11329,7 +11329,7 @@
         <v>乌索克庇护</v>
       </c>
       <c r="C80" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-ursoc-shelter</v>
       </c>
       <c r="D80" t="str">
         <v>talent</v>
@@ -11346,7 +11346,7 @@
         <v>水火不侵</v>
       </c>
       <c r="C81" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-water-fire-immunity</v>
       </c>
       <c r="D81" t="str">
         <v>talent</v>
@@ -11363,7 +11363,7 @@
         <v>兽群愈合</v>
       </c>
       <c r="C82" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-regrowth-of-the-pack</v>
       </c>
       <c r="D82" t="str">
         <v>talent</v>
@@ -11380,7 +11380,7 @@
         <v>林地守护者</v>
       </c>
       <c r="C83" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-guardian-of-the-grove</v>
       </c>
       <c r="D83" t="str">
         <v>talent</v>
@@ -11397,7 +11397,7 @@
         <v>野性余震</v>
       </c>
       <c r="C84" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-feral-aftershock</v>
       </c>
       <c r="D84" t="str">
         <v>talent</v>
@@ -11414,7 +11414,7 @@
         <v>巨熊绝境</v>
       </c>
       <c r="C85" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-last-bear-stand</v>
       </c>
       <c r="D85" t="str">
         <v>talent</v>
@@ -11431,7 +11431,7 @@
         <v>春风吹又生</v>
       </c>
       <c r="C86" t="str">
-        <v>bear-leaf</v>
+        <v>bear-talent-spring-returns</v>
       </c>
       <c r="D86" t="str">
         <v>talent</v>
@@ -11448,7 +11448,7 @@
         <v>铁鬃</v>
       </c>
       <c r="C87" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-ironfur</v>
       </c>
       <c r="D87" t="str">
         <v>status</v>
@@ -11465,7 +11465,7 @@
         <v>狂暴回复</v>
       </c>
       <c r="C88" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-frenzied-regeneration</v>
       </c>
       <c r="D88" t="str">
         <v>status</v>
@@ -11482,7 +11482,7 @@
         <v>月火术</v>
       </c>
       <c r="C89" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-moonfire</v>
       </c>
       <c r="D89" t="str">
         <v>status</v>
@@ -11499,7 +11499,7 @@
         <v>树皮术</v>
       </c>
       <c r="C90" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-barkskin</v>
       </c>
       <c r="D90" t="str">
         <v>status</v>
@@ -11516,7 +11516,7 @@
         <v>生存本能</v>
       </c>
       <c r="C91" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-survival-instincts</v>
       </c>
       <c r="D91" t="str">
         <v>status</v>
@@ -11533,7 +11533,7 @@
         <v>明月普照</v>
       </c>
       <c r="C92" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-lunar-beam</v>
       </c>
       <c r="D92" t="str">
         <v>status</v>
@@ -11550,7 +11550,7 @@
         <v>乌索克的化身</v>
       </c>
       <c r="C93" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-incarnation-ursoc</v>
       </c>
       <c r="D93" t="str">
         <v>status</v>
@@ -11567,7 +11567,7 @@
         <v>沉睡者之怒</v>
       </c>
       <c r="C94" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-rage-of-the-sleeper</v>
       </c>
       <c r="D94" t="str">
         <v>status</v>
@@ -11584,7 +11584,7 @@
         <v>愈合</v>
       </c>
       <c r="C95" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-regrowth</v>
       </c>
       <c r="D95" t="str">
         <v>status</v>
@@ -11635,7 +11635,7 @@
         <v>月下坚守</v>
       </c>
       <c r="C98" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-moonlit-resolve</v>
       </c>
       <c r="D98" t="str">
         <v>status</v>
@@ -11652,7 +11652,7 @@
         <v>乌索克庇护</v>
       </c>
       <c r="C99" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-ursoc-shelter</v>
       </c>
       <c r="D99" t="str">
         <v>status</v>
@@ -11669,7 +11669,7 @@
         <v>野性复原</v>
       </c>
       <c r="C100" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-wild-recovery</v>
       </c>
       <c r="D100" t="str">
         <v>status</v>
@@ -11686,7 +11686,7 @@
         <v>野性余震</v>
       </c>
       <c r="C101" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-feral-aftershock</v>
       </c>
       <c r="D101" t="str">
         <v>status</v>
@@ -11703,7 +11703,7 @@
         <v>林地守护者</v>
       </c>
       <c r="C102" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-guardian-of-the-grove</v>
       </c>
       <c r="D102" t="str">
         <v>status</v>
@@ -11720,7 +11720,7 @@
         <v>痛苦之怒</v>
       </c>
       <c r="C103" t="str">
-        <v>bear-pain-rage</v>
+        <v>bear-talent-pain-rage</v>
       </c>
       <c r="D103" t="str">
         <v>talent</v>
@@ -11737,7 +11737,7 @@
         <v>怒气枯竭</v>
       </c>
       <c r="C104" t="str">
-        <v>bear-rage-lock</v>
+        <v>bear-status-rage-exhaustion</v>
       </c>
       <c r="D104" t="str">
         <v>status</v>
@@ -11754,7 +11754,7 @@
         <v>疼痛豁免护盾</v>
       </c>
       <c r="C105" t="str">
-        <v>bear-aura</v>
+        <v>bear-status-pain-immunity</v>
       </c>
       <c r="D105" t="str">
         <v>status</v>
